--- a/api/clv2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/clv2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,36 +139,39 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
@@ -178,30 +181,27 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,18 +811,21 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
@@ -832,21 +835,18 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,6 +991,9 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
@@ -1000,9 +1003,6 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,6 +1105,9 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
@@ -1114,9 +1117,6 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1935,10 +1935,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1955,10 +1955,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1981,10 +1981,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -2004,10 +2004,10 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2027,16 +2027,16 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,13 +2047,13 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,13 +2116,13 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2142,10 +2142,10 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2162,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -2231,13 +2231,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>32</v>
@@ -2254,13 +2254,13 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
@@ -2300,13 +2300,13 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>64</v>
       </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>32</v>
@@ -2323,13 +2323,13 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
         <v>32</v>
@@ -2346,13 +2346,13 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
         <v>64</v>
       </c>
-      <c r="D24" t="s">
-        <v>52</v>
-      </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
@@ -2369,13 +2369,13 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
         <v>64</v>
       </c>
-      <c r="D25" t="s">
-        <v>52</v>
-      </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
@@ -2392,13 +2392,13 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
         <v>64</v>
       </c>
-      <c r="D26" t="s">
-        <v>52</v>
-      </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
@@ -2415,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
         <v>64</v>
       </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -2438,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
         <v>64</v>
       </c>
-      <c r="D28" t="s">
-        <v>52</v>
-      </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2461,13 +2461,13 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
         <v>64</v>
       </c>
-      <c r="D29" t="s">
-        <v>52</v>
-      </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
         <v>32</v>
@@ -2484,10 +2484,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" t="s">
         <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>52</v>
       </c>
       <c r="E30" t="s">
         <v>53</v>
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
         <v>76</v>
       </c>
-      <c r="D31" t="s">
-        <v>52</v>
-      </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2530,13 +2530,13 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
         <v>76</v>
       </c>
-      <c r="D32" t="s">
-        <v>52</v>
-      </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2553,13 +2553,13 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
         <v>76</v>
       </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2576,13 +2576,13 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
         <v>76</v>
       </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -2599,13 +2599,13 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
         <v>76</v>
       </c>
-      <c r="D35" t="s">
-        <v>52</v>
-      </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -2622,13 +2622,13 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
         <v>76</v>
       </c>
-      <c r="D36" t="s">
-        <v>52</v>
-      </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
         <v>32</v>
@@ -2644,11 +2644,11 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="D37" t="s">
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
         <v>83</v>
-      </c>
-      <c r="E37" t="s">
-        <v>31</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
@@ -2664,11 +2664,11 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
       </c>
       <c r="F38" t="s">
         <v>32</v>
@@ -2684,11 +2684,11 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="D39" t="s">
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
         <v>83</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
       </c>
       <c r="F39" t="s">
         <v>32</v>
@@ -2704,11 +2704,11 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
         <v>83</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>32</v>
@@ -2724,11 +2724,11 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="D41" t="s">
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
         <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>53</v>
       </c>
       <c r="F41" t="s">
         <v>32</v>
@@ -2744,11 +2744,11 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" t="s">
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
         <v>83</v>
-      </c>
-      <c r="E42" t="s">
-        <v>57</v>
       </c>
       <c r="F42" t="s">
         <v>32</v>
@@ -2764,7 +2764,7 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="D43" t="s">
+      <c r="C43" t="s">
         <v>90</v>
       </c>
       <c r="E43" t="s">
@@ -2784,11 +2784,11 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="D44" t="s">
-        <v>90</v>
+      <c r="C44" t="s">
+        <v>95</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
         <v>96</v>
@@ -2804,7 +2804,7 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="D45" t="s">
+      <c r="C45" t="s">
         <v>90</v>
       </c>
       <c r="E45" t="s">
@@ -2824,7 +2824,7 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="D46" t="s">
+      <c r="C46" t="s">
         <v>90</v>
       </c>
       <c r="E46" t="s">
@@ -2844,11 +2844,11 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="D47" t="s">
-        <v>90</v>
+      <c r="C47" t="s">
+        <v>101</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
         <v>96</v>
@@ -2864,7 +2864,7 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="D48" t="s">
+      <c r="C48" t="s">
         <v>90</v>
       </c>
       <c r="E48" t="s">
@@ -2884,7 +2884,7 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="D49" t="s">
+      <c r="C49" t="s">
         <v>90</v>
       </c>
       <c r="E49" t="s">
@@ -2904,11 +2904,11 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="D50" t="s">
-        <v>90</v>
+      <c r="C50" t="s">
+        <v>101</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F50" t="s">
         <v>96</v>
@@ -2924,7 +2924,7 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="D51" t="s">
+      <c r="C51" t="s">
         <v>90</v>
       </c>
       <c r="E51" t="s">
@@ -2944,11 +2944,11 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="D52" t="s">
-        <v>90</v>
+      <c r="C52" t="s">
+        <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F52" t="s">
         <v>96</v>
@@ -2964,11 +2964,11 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="D53" t="s">
-        <v>90</v>
+      <c r="C53" t="s">
+        <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -3008,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
         <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3031,13 +3031,13 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
         <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3054,13 +3054,13 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
         <v>113</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>125</v>
@@ -3077,13 +3077,13 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3123,13 +3123,13 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3146,13 +3146,13 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3169,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
         <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,13 +3238,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3284,13 +3284,13 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3313,13 +3313,13 @@
         <v>113</v>
       </c>
       <c r="E68" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3336,13 +3336,13 @@
         <v>113</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3422,13 +3422,13 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
         <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
         <v>125</v>
@@ -3445,13 +3445,13 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
         <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
         <v>125</v>
@@ -3468,13 +3468,13 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
         <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F75" t="s">
         <v>125</v>
@@ -3491,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
         <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F76" t="s">
         <v>125</v>
@@ -3514,13 +3514,13 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
         <v>125</v>
@@ -3537,13 +3537,13 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
         <v>125</v>
@@ -3560,13 +3560,13 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
         <v>113</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
         <v>125</v>
@@ -3583,13 +3583,13 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
         <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>164</v>
@@ -3606,13 +3606,13 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
         <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
         <v>164</v>
@@ -3629,13 +3629,13 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
         <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
         <v>164</v>
@@ -3658,13 +3658,13 @@
         <v>113</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F83" t="s">
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3675,13 +3675,13 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
         <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,13 +3721,13 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
         <v>164</v>
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
         <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3790,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
         <v>113</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3813,13 +3813,13 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
         <v>113</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
         <v>125</v>
@@ -3836,13 +3836,13 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
         <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
         <v>183</v>
@@ -3859,13 +3859,13 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
         <v>125</v>
@@ -3882,13 +3882,13 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
         <v>113</v>
       </c>
       <c r="E93" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3905,13 +3905,13 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
         <v>113</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F94" t="s">
         <v>125</v>
@@ -3928,13 +3928,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
         <v>113</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3951,13 +3951,13 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" t="s">
         <v>192</v>
       </c>
-      <c r="D96" t="s">
-        <v>113</v>
-      </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F96" t="s">
         <v>125</v>
@@ -3974,13 +3974,13 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97" t="s">
         <v>192</v>
       </c>
-      <c r="D97" t="s">
-        <v>113</v>
-      </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
         <v>125</v>
@@ -3997,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" t="s">
         <v>192</v>
       </c>
-      <c r="D98" t="s">
-        <v>113</v>
-      </c>
       <c r="E98" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
         <v>196</v>
@@ -4020,13 +4020,13 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" t="s">
         <v>192</v>
       </c>
-      <c r="D99" t="s">
-        <v>113</v>
-      </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
         <v>125</v>
@@ -4043,13 +4043,13 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>154</v>
+      </c>
+      <c r="D100" t="s">
         <v>192</v>
       </c>
-      <c r="D100" t="s">
-        <v>113</v>
-      </c>
       <c r="E100" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F100" t="s">
         <v>125</v>
@@ -4066,13 +4066,13 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101" t="s">
         <v>192</v>
       </c>
-      <c r="D101" t="s">
-        <v>113</v>
-      </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s">
         <v>125</v>
@@ -4088,7 +4088,7 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="D102" t="s">
+      <c r="C102" t="s">
         <v>202</v>
       </c>
       <c r="E102" t="s">
@@ -4108,7 +4108,7 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="D103" t="s">
+      <c r="C103" t="s">
         <v>202</v>
       </c>
       <c r="E103" t="s">
@@ -4128,7 +4128,7 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="D104" t="s">
+      <c r="C104" t="s">
         <v>202</v>
       </c>
       <c r="E104" t="s">
@@ -4148,11 +4148,11 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="D105" t="s">
-        <v>202</v>
+      <c r="C105" t="s">
+        <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F105" t="s">
         <v>183</v>
@@ -4168,7 +4168,7 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="D106" t="s">
+      <c r="C106" t="s">
         <v>202</v>
       </c>
       <c r="E106" t="s">
@@ -4188,11 +4188,11 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="D107" t="s">
-        <v>202</v>
+      <c r="C107" t="s">
+        <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>183</v>
@@ -4208,11 +4208,11 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="D108" t="s">
-        <v>202</v>
+      <c r="C108" t="s">
+        <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
         <v>183</v>
@@ -4228,11 +4228,11 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="D109" t="s">
-        <v>202</v>
+      <c r="C109" t="s">
+        <v>216</v>
       </c>
       <c r="E109" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
         <v>92</v>
@@ -4248,11 +4248,11 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="D110" t="s">
-        <v>202</v>
+      <c r="C110" t="s">
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
         <v>92</v>
@@ -4268,7 +4268,7 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="D111" t="s">
+      <c r="C111" t="s">
         <v>202</v>
       </c>
       <c r="E111" t="s">
@@ -4288,11 +4288,11 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="D112" t="s">
-        <v>202</v>
+      <c r="C112" t="s">
+        <v>223</v>
       </c>
       <c r="E112" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
         <v>224</v>
@@ -4308,17 +4308,17 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="D113" t="s">
-        <v>202</v>
+      <c r="C113" t="s">
+        <v>112</v>
       </c>
       <c r="E113" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4328,11 +4328,11 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="D114" t="s">
-        <v>202</v>
+      <c r="C114" t="s">
+        <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
         <v>125</v>
@@ -4348,11 +4348,11 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="D115" t="s">
-        <v>202</v>
+      <c r="C115" t="s">
+        <v>182</v>
       </c>
       <c r="E115" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
         <v>183</v>
@@ -4368,11 +4368,11 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="D116" t="s">
-        <v>202</v>
+      <c r="C116" t="s">
+        <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="F116" t="s">
         <v>224</v>
@@ -4388,11 +4388,11 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="D117" t="s">
-        <v>202</v>
+      <c r="C117" t="s">
+        <v>223</v>
       </c>
       <c r="E117" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="F117" t="s">
         <v>224</v>
@@ -4408,17 +4408,17 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="D118" t="s">
-        <v>202</v>
+      <c r="C118" t="s">
+        <v>163</v>
       </c>
       <c r="E118" t="s">
+        <v>203</v>
+      </c>
+      <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
-      </c>
-      <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4428,11 +4428,11 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="D119" t="s">
-        <v>202</v>
+      <c r="C119" t="s">
+        <v>182</v>
       </c>
       <c r="E119" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>183</v>
@@ -4448,11 +4448,11 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="D120" t="s">
+      <c r="C120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s">
         <v>237</v>
-      </c>
-      <c r="E120" t="s">
-        <v>170</v>
       </c>
       <c r="F120" t="s">
         <v>115</v>
@@ -4468,17 +4468,17 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="D121" t="s">
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="E121" t="s">
         <v>237</v>
-      </c>
-      <c r="E121" t="s">
-        <v>143</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4488,11 +4488,11 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="D122" t="s">
+      <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="E122" t="s">
         <v>237</v>
-      </c>
-      <c r="E122" t="s">
-        <v>170</v>
       </c>
       <c r="F122" t="s">
         <v>115</v>
@@ -4508,11 +4508,11 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="D123" t="s">
+      <c r="C123" t="s">
+        <v>170</v>
+      </c>
+      <c r="E123" t="s">
         <v>237</v>
-      </c>
-      <c r="E123" t="s">
-        <v>170</v>
       </c>
       <c r="F123" t="s">
         <v>115</v>
@@ -4528,11 +4528,11 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="D124" t="s">
+      <c r="C124" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" t="s">
         <v>237</v>
-      </c>
-      <c r="E124" t="s">
-        <v>242</v>
       </c>
       <c r="F124" t="s">
         <v>164</v>
@@ -4548,11 +4548,11 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="D125" t="s">
+      <c r="C125" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s">
         <v>237</v>
-      </c>
-      <c r="E125" t="s">
-        <v>242</v>
       </c>
       <c r="F125" t="s">
         <v>164</v>
@@ -4568,11 +4568,11 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="D126" t="s">
+      <c r="C126" t="s">
+        <v>242</v>
+      </c>
+      <c r="E126" t="s">
         <v>237</v>
-      </c>
-      <c r="E126" t="s">
-        <v>242</v>
       </c>
       <c r="F126" t="s">
         <v>164</v>
@@ -4588,11 +4588,11 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="D127" t="s">
+      <c r="C127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
         <v>237</v>
-      </c>
-      <c r="E127" t="s">
-        <v>242</v>
       </c>
       <c r="F127" t="s">
         <v>164</v>
@@ -4608,11 +4608,11 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="D128" t="s">
+      <c r="C128" t="s">
+        <v>242</v>
+      </c>
+      <c r="E128" t="s">
         <v>237</v>
-      </c>
-      <c r="E128" t="s">
-        <v>242</v>
       </c>
       <c r="F128" t="s">
         <v>164</v>
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="D129" t="s">
+      <c r="C129" t="s">
+        <v>242</v>
+      </c>
+      <c r="E129" t="s">
         <v>237</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
+        <v>164</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="F129" t="s">
-        <v>164</v>
-      </c>
-      <c r="G129" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="D130" t="s">
+      <c r="C130" t="s">
+        <v>242</v>
+      </c>
+      <c r="E130" t="s">
         <v>237</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="F130" t="s">
-        <v>164</v>
-      </c>
-      <c r="G130" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="D131" t="s">
+      <c r="C131" t="s">
+        <v>242</v>
+      </c>
+      <c r="E131" t="s">
         <v>237</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="F131" t="s">
-        <v>164</v>
-      </c>
-      <c r="G131" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,11 +4688,11 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="D132" t="s">
+      <c r="C132" t="s">
+        <v>255</v>
+      </c>
+      <c r="E132" t="s">
         <v>237</v>
-      </c>
-      <c r="E132" t="s">
-        <v>255</v>
       </c>
       <c r="F132" t="s">
         <v>164</v>
@@ -4708,11 +4708,11 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="D133" t="s">
+      <c r="C133" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" t="s">
         <v>237</v>
-      </c>
-      <c r="E133" t="s">
-        <v>189</v>
       </c>
       <c r="F133" t="s">
         <v>115</v>
@@ -4728,11 +4728,11 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="D134" t="s">
+      <c r="C134" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" t="s">
         <v>259</v>
-      </c>
-      <c r="E134" t="s">
-        <v>175</v>
       </c>
       <c r="F134" t="s">
         <v>164</v>
@@ -4748,11 +4748,11 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="D135" t="s">
+      <c r="C135" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" t="s">
         <v>259</v>
-      </c>
-      <c r="E135" t="s">
-        <v>175</v>
       </c>
       <c r="F135" t="s">
         <v>164</v>
@@ -4768,11 +4768,11 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="D136" t="s">
+      <c r="C136" t="s">
+        <v>175</v>
+      </c>
+      <c r="E136" t="s">
         <v>259</v>
-      </c>
-      <c r="E136" t="s">
-        <v>175</v>
       </c>
       <c r="F136" t="s">
         <v>164</v>
@@ -4788,11 +4788,11 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="D137" t="s">
+      <c r="C137" t="s">
+        <v>175</v>
+      </c>
+      <c r="E137" t="s">
         <v>259</v>
-      </c>
-      <c r="E137" t="s">
-        <v>175</v>
       </c>
       <c r="F137" t="s">
         <v>164</v>
@@ -4808,11 +4808,11 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="D138" t="s">
+      <c r="C138" t="s">
+        <v>175</v>
+      </c>
+      <c r="E138" t="s">
         <v>259</v>
-      </c>
-      <c r="E138" t="s">
-        <v>175</v>
       </c>
       <c r="F138" t="s">
         <v>164</v>
@@ -4828,11 +4828,11 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="D139" t="s">
+      <c r="C139" t="s">
+        <v>265</v>
+      </c>
+      <c r="E139" t="s">
         <v>259</v>
-      </c>
-      <c r="E139" t="s">
-        <v>265</v>
       </c>
       <c r="F139" t="s">
         <v>224</v>
@@ -4848,11 +4848,11 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="D140" t="s">
+      <c r="C140" t="s">
+        <v>175</v>
+      </c>
+      <c r="E140" t="s">
         <v>259</v>
-      </c>
-      <c r="E140" t="s">
-        <v>175</v>
       </c>
       <c r="F140" t="s">
         <v>164</v>
@@ -4915,13 +4915,13 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
         <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
         <v>164</v>
@@ -4938,13 +4938,13 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
         <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
         <v>164</v>
@@ -4961,13 +4961,13 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
         <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
         <v>164</v>
@@ -5007,10 +5007,10 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>269</v>
+      </c>
+      <c r="D147" t="s">
         <v>281</v>
-      </c>
-      <c r="D147" t="s">
-        <v>270</v>
       </c>
       <c r="E147" t="s">
         <v>271</v>
@@ -5030,10 +5030,10 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>269</v>
+      </c>
+      <c r="D148" t="s">
         <v>281</v>
-      </c>
-      <c r="D148" t="s">
-        <v>270</v>
       </c>
       <c r="E148" t="s">
         <v>271</v>
@@ -5053,10 +5053,10 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>269</v>
+      </c>
+      <c r="D149" t="s">
         <v>281</v>
-      </c>
-      <c r="D149" t="s">
-        <v>270</v>
       </c>
       <c r="E149" t="s">
         <v>271</v>
@@ -5076,10 +5076,10 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>269</v>
+      </c>
+      <c r="D150" t="s">
         <v>281</v>
-      </c>
-      <c r="D150" t="s">
-        <v>270</v>
       </c>
       <c r="E150" t="s">
         <v>271</v>
@@ -5099,10 +5099,10 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>269</v>
+      </c>
+      <c r="D151" t="s">
         <v>281</v>
-      </c>
-      <c r="D151" t="s">
-        <v>270</v>
       </c>
       <c r="E151" t="s">
         <v>271</v>
@@ -5122,10 +5122,10 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>269</v>
+      </c>
+      <c r="D152" t="s">
         <v>281</v>
-      </c>
-      <c r="D152" t="s">
-        <v>270</v>
       </c>
       <c r="E152" t="s">
         <v>271</v>
@@ -5145,10 +5145,10 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>269</v>
+      </c>
+      <c r="D153" t="s">
         <v>281</v>
-      </c>
-      <c r="D153" t="s">
-        <v>270</v>
       </c>
       <c r="E153" t="s">
         <v>271</v>
@@ -5168,10 +5168,10 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>269</v>
+      </c>
+      <c r="D154" t="s">
         <v>281</v>
-      </c>
-      <c r="D154" t="s">
-        <v>270</v>
       </c>
       <c r="E154" t="s">
         <v>271</v>
@@ -5191,10 +5191,10 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>269</v>
+      </c>
+      <c r="D155" t="s">
         <v>281</v>
-      </c>
-      <c r="D155" t="s">
-        <v>270</v>
       </c>
       <c r="E155" t="s">
         <v>271</v>
@@ -5214,10 +5214,10 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>269</v>
+      </c>
+      <c r="D156" t="s">
         <v>291</v>
-      </c>
-      <c r="D156" t="s">
-        <v>270</v>
       </c>
       <c r="E156" t="s">
         <v>271</v>
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>269</v>
+      </c>
+      <c r="D157" t="s">
         <v>291</v>
       </c>
-      <c r="D157" t="s">
-        <v>270</v>
-      </c>
       <c r="E157" t="s">
+        <v>271</v>
+      </c>
+      <c r="F157" t="s">
+        <v>164</v>
+      </c>
+      <c r="G157" t="s">
         <v>293</v>
-      </c>
-      <c r="F157" t="s">
-        <v>164</v>
-      </c>
-      <c r="G157" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,10 +5260,10 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>269</v>
+      </c>
+      <c r="D158" t="s">
         <v>291</v>
-      </c>
-      <c r="D158" t="s">
-        <v>270</v>
       </c>
       <c r="E158" t="s">
         <v>271</v>
@@ -5283,10 +5283,10 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>269</v>
+      </c>
+      <c r="D159" t="s">
         <v>291</v>
-      </c>
-      <c r="D159" t="s">
-        <v>270</v>
       </c>
       <c r="E159" t="s">
         <v>271</v>
@@ -5306,10 +5306,10 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>269</v>
+      </c>
+      <c r="D160" t="s">
         <v>291</v>
-      </c>
-      <c r="D160" t="s">
-        <v>270</v>
       </c>
       <c r="E160" t="s">
         <v>271</v>
@@ -5329,10 +5329,10 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>269</v>
+      </c>
+      <c r="D161" t="s">
         <v>291</v>
-      </c>
-      <c r="D161" t="s">
-        <v>270</v>
       </c>
       <c r="E161" t="s">
         <v>271</v>
@@ -5352,10 +5352,10 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>269</v>
+      </c>
+      <c r="D162" t="s">
         <v>299</v>
-      </c>
-      <c r="D162" t="s">
-        <v>270</v>
       </c>
       <c r="E162" t="s">
         <v>271</v>
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>270</v>
-      </c>
       <c r="E163" t="s">
+        <v>271</v>
+      </c>
+      <c r="F163" t="s">
+        <v>164</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="F163" t="s">
-        <v>164</v>
-      </c>
-      <c r="G163" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,10 +5398,10 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>269</v>
+      </c>
+      <c r="D164" t="s">
         <v>304</v>
-      </c>
-      <c r="D164" t="s">
-        <v>270</v>
       </c>
       <c r="E164" t="s">
         <v>271</v>
@@ -5421,10 +5421,10 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>269</v>
+      </c>
+      <c r="D165" t="s">
         <v>304</v>
-      </c>
-      <c r="D165" t="s">
-        <v>270</v>
       </c>
       <c r="E165" t="s">
         <v>271</v>
@@ -5444,10 +5444,10 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>269</v>
+      </c>
+      <c r="D166" t="s">
         <v>304</v>
-      </c>
-      <c r="D166" t="s">
-        <v>270</v>
       </c>
       <c r="E166" t="s">
         <v>271</v>
@@ -5467,10 +5467,10 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>269</v>
+      </c>
+      <c r="D167" t="s">
         <v>304</v>
-      </c>
-      <c r="D167" t="s">
-        <v>270</v>
       </c>
       <c r="E167" t="s">
         <v>271</v>
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>269</v>
+      </c>
+      <c r="D168" t="s">
         <v>304</v>
       </c>
-      <c r="D168" t="s">
-        <v>270</v>
-      </c>
       <c r="E168" t="s">
+        <v>271</v>
+      </c>
+      <c r="F168" t="s">
+        <v>164</v>
+      </c>
+      <c r="G168" t="s">
         <v>309</v>
-      </c>
-      <c r="F168" t="s">
-        <v>164</v>
-      </c>
-      <c r="G168" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>269</v>
+      </c>
+      <c r="D169" t="s">
         <v>304</v>
       </c>
-      <c r="D169" t="s">
-        <v>270</v>
-      </c>
       <c r="E169" t="s">
+        <v>271</v>
+      </c>
+      <c r="F169" t="s">
+        <v>164</v>
+      </c>
+      <c r="G169" t="s">
         <v>309</v>
-      </c>
-      <c r="F169" t="s">
-        <v>164</v>
-      </c>
-      <c r="G169" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,10 +5536,10 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>269</v>
+      </c>
+      <c r="D170" t="s">
         <v>304</v>
-      </c>
-      <c r="D170" t="s">
-        <v>270</v>
       </c>
       <c r="E170" t="s">
         <v>271</v>
@@ -5558,11 +5558,11 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="D171" t="s">
+      <c r="C171" t="s">
+        <v>163</v>
+      </c>
+      <c r="E171" t="s">
         <v>313</v>
-      </c>
-      <c r="E171" t="s">
-        <v>163</v>
       </c>
       <c r="F171" t="s">
         <v>164</v>
@@ -5578,11 +5578,11 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="D172" t="s">
+      <c r="C172" t="s">
+        <v>118</v>
+      </c>
+      <c r="E172" t="s">
         <v>313</v>
-      </c>
-      <c r="E172" t="s">
-        <v>118</v>
       </c>
       <c r="F172" t="s">
         <v>115</v>
@@ -5598,11 +5598,11 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="D173" t="s">
+      <c r="C173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s">
         <v>313</v>
-      </c>
-      <c r="E173" t="s">
-        <v>163</v>
       </c>
       <c r="F173" t="s">
         <v>164</v>
@@ -5618,11 +5618,11 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="D174" t="s">
+      <c r="C174" t="s">
+        <v>163</v>
+      </c>
+      <c r="E174" t="s">
         <v>313</v>
-      </c>
-      <c r="E174" t="s">
-        <v>163</v>
       </c>
       <c r="F174" t="s">
         <v>164</v>
@@ -5638,11 +5638,11 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="D175" t="s">
+      <c r="C175" t="s">
+        <v>163</v>
+      </c>
+      <c r="E175" t="s">
         <v>313</v>
-      </c>
-      <c r="E175" t="s">
-        <v>163</v>
       </c>
       <c r="F175" t="s">
         <v>164</v>
@@ -5658,11 +5658,11 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="D176" t="s">
+      <c r="C176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" t="s">
         <v>313</v>
-      </c>
-      <c r="E176" t="s">
-        <v>163</v>
       </c>
       <c r="F176" t="s">
         <v>164</v>
@@ -5678,11 +5678,11 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="D177" t="s">
+      <c r="C177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
         <v>320</v>
-      </c>
-      <c r="E177" t="s">
-        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>164</v>
@@ -5698,11 +5698,11 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="D178" t="s">
+      <c r="C178" t="s">
+        <v>163</v>
+      </c>
+      <c r="E178" t="s">
         <v>320</v>
-      </c>
-      <c r="E178" t="s">
-        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>164</v>
@@ -5718,11 +5718,11 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="D179" t="s">
+      <c r="C179" t="s">
+        <v>163</v>
+      </c>
+      <c r="E179" t="s">
         <v>320</v>
-      </c>
-      <c r="E179" t="s">
-        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>164</v>
@@ -5738,11 +5738,11 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="D180" t="s">
+      <c r="C180" t="s">
+        <v>163</v>
+      </c>
+      <c r="E180" t="s">
         <v>320</v>
-      </c>
-      <c r="E180" t="s">
-        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>164</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
       </c>
       <c r="E193" t="s">
+        <v>327</v>
+      </c>
+      <c r="F193" t="s">
+        <v>164</v>
+      </c>
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="F193" t="s">
-        <v>164</v>
-      </c>
-      <c r="G193" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>325</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>326</v>
-      </c>
       <c r="E199" t="s">
+        <v>327</v>
+      </c>
+      <c r="F199" t="s">
+        <v>164</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="F199" t="s">
-        <v>164</v>
-      </c>
-      <c r="G199" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>325</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>326</v>
-      </c>
       <c r="E200" t="s">
+        <v>327</v>
+      </c>
+      <c r="F200" t="s">
+        <v>164</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="F200" t="s">
-        <v>164</v>
-      </c>
-      <c r="G200" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>325</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>326</v>
-      </c>
       <c r="E201" t="s">
+        <v>327</v>
+      </c>
+      <c r="F201" t="s">
+        <v>164</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="F201" t="s">
-        <v>164</v>
-      </c>
-      <c r="G201" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>326</v>
-      </c>
       <c r="E202" t="s">
+        <v>327</v>
+      </c>
+      <c r="F202" t="s">
+        <v>164</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="F202" t="s">
-        <v>164</v>
-      </c>
-      <c r="G202" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>275</v>
+      </c>
+      <c r="D203" t="s">
         <v>348</v>
       </c>
-      <c r="D203" t="s">
-        <v>326</v>
-      </c>
       <c r="E203" t="s">
+        <v>327</v>
+      </c>
+      <c r="F203" t="s">
+        <v>164</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="F203" t="s">
-        <v>164</v>
-      </c>
-      <c r="G203" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>326</v>
-      </c>
       <c r="E204" t="s">
+        <v>327</v>
+      </c>
+      <c r="F204" t="s">
+        <v>164</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="F204" t="s">
-        <v>164</v>
-      </c>
-      <c r="G204" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>326</v>
-      </c>
       <c r="E205" t="s">
+        <v>327</v>
+      </c>
+      <c r="F205" t="s">
+        <v>164</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="F205" t="s">
-        <v>164</v>
-      </c>
-      <c r="G205" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>325</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>326</v>
-      </c>
       <c r="E206" t="s">
+        <v>327</v>
+      </c>
+      <c r="F206" t="s">
+        <v>164</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="F206" t="s">
-        <v>164</v>
-      </c>
-      <c r="G206" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>325</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>326</v>
-      </c>
       <c r="E207" t="s">
+        <v>327</v>
+      </c>
+      <c r="F207" t="s">
+        <v>164</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="F207" t="s">
-        <v>164</v>
-      </c>
-      <c r="G207" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" t="s">
         <v>356</v>
       </c>
-      <c r="D208" t="s">
-        <v>326</v>
-      </c>
       <c r="E208" t="s">
+        <v>327</v>
+      </c>
+      <c r="F208" t="s">
+        <v>164</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="F208" t="s">
-        <v>164</v>
-      </c>
-      <c r="G208" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>326</v>
-      </c>
       <c r="E209" t="s">
+        <v>327</v>
+      </c>
+      <c r="F209" t="s">
+        <v>164</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="F209" t="s">
-        <v>164</v>
-      </c>
-      <c r="G209" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
         <v>364</v>
       </c>
       <c r="E215" t="s">
+        <v>365</v>
+      </c>
+      <c r="F215" t="s">
+        <v>164</v>
+      </c>
+      <c r="G215" t="s">
         <v>349</v>
-      </c>
-      <c r="F215" t="s">
-        <v>164</v>
-      </c>
-      <c r="G215" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
         <v>364</v>
       </c>
       <c r="E220" t="s">
+        <v>365</v>
+      </c>
+      <c r="F220" t="s">
+        <v>164</v>
+      </c>
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="F220" t="s">
-        <v>164</v>
-      </c>
-      <c r="G220" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6794,13 +6794,13 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
         <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="F226" t="s">
         <v>164</v>
@@ -6840,13 +6840,13 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
         <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="F228" t="s">
         <v>164</v>
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>364</v>
-      </c>
       <c r="E229" t="s">
+        <v>365</v>
+      </c>
+      <c r="F229" t="s">
+        <v>164</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="F229" t="s">
-        <v>164</v>
-      </c>
-      <c r="G229" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>363</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>364</v>
-      </c>
       <c r="E230" t="s">
+        <v>365</v>
+      </c>
+      <c r="F230" t="s">
+        <v>164</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="F230" t="s">
-        <v>164</v>
-      </c>
-      <c r="G230" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>269</v>
+      </c>
+      <c r="D231" t="s">
         <v>386</v>
       </c>
-      <c r="D231" t="s">
-        <v>364</v>
-      </c>
       <c r="E231" t="s">
+        <v>365</v>
+      </c>
+      <c r="F231" t="s">
+        <v>164</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="F231" t="s">
-        <v>164</v>
-      </c>
-      <c r="G231" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>269</v>
+      </c>
+      <c r="D232" t="s">
         <v>386</v>
       </c>
-      <c r="D232" t="s">
-        <v>364</v>
-      </c>
       <c r="E232" t="s">
+        <v>365</v>
+      </c>
+      <c r="F232" t="s">
+        <v>164</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="F232" t="s">
-        <v>164</v>
-      </c>
-      <c r="G232" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>363</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>364</v>
-      </c>
       <c r="E233" t="s">
+        <v>365</v>
+      </c>
+      <c r="F233" t="s">
+        <v>164</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="F233" t="s">
-        <v>164</v>
-      </c>
-      <c r="G233" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>364</v>
-      </c>
       <c r="E234" t="s">
+        <v>365</v>
+      </c>
+      <c r="F234" t="s">
+        <v>164</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="F234" t="s">
-        <v>164</v>
-      </c>
-      <c r="G234" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>363</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>364</v>
-      </c>
       <c r="E235" t="s">
+        <v>365</v>
+      </c>
+      <c r="F235" t="s">
+        <v>164</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="F235" t="s">
-        <v>164</v>
-      </c>
-      <c r="G235" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>363</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>364</v>
-      </c>
       <c r="E236" t="s">
+        <v>365</v>
+      </c>
+      <c r="F236" t="s">
+        <v>164</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="F236" t="s">
-        <v>164</v>
-      </c>
-      <c r="G236" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>363</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>364</v>
-      </c>
       <c r="E237" t="s">
+        <v>365</v>
+      </c>
+      <c r="F237" t="s">
+        <v>164</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="F237" t="s">
-        <v>164</v>
-      </c>
-      <c r="G237" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>363</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>364</v>
-      </c>
       <c r="E238" t="s">
+        <v>365</v>
+      </c>
+      <c r="F238" t="s">
+        <v>164</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="F238" t="s">
-        <v>164</v>
-      </c>
-      <c r="G238" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>363</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>364</v>
-      </c>
       <c r="E239" t="s">
+        <v>365</v>
+      </c>
+      <c r="F239" t="s">
+        <v>164</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="F239" t="s">
-        <v>164</v>
-      </c>
-      <c r="G239" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,13 +7116,13 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
         <v>402</v>
-      </c>
-      <c r="E240" t="s">
-        <v>163</v>
       </c>
       <c r="F240" t="s">
         <v>164</v>
@@ -7139,13 +7139,13 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
         <v>402</v>
-      </c>
-      <c r="E241" t="s">
-        <v>163</v>
       </c>
       <c r="F241" t="s">
         <v>164</v>
@@ -7162,13 +7162,13 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
         <v>402</v>
-      </c>
-      <c r="E242" t="s">
-        <v>163</v>
       </c>
       <c r="F242" t="s">
         <v>164</v>
@@ -7185,13 +7185,13 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
         <v>402</v>
-      </c>
-      <c r="E243" t="s">
-        <v>163</v>
       </c>
       <c r="F243" t="s">
         <v>164</v>
@@ -7208,13 +7208,13 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
+      <c r="E244" t="s">
         <v>402</v>
-      </c>
-      <c r="E244" t="s">
-        <v>163</v>
       </c>
       <c r="F244" t="s">
         <v>164</v>
@@ -7231,13 +7231,13 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
+      <c r="E245" t="s">
         <v>402</v>
-      </c>
-      <c r="E245" t="s">
-        <v>163</v>
       </c>
       <c r="F245" t="s">
         <v>164</v>
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
         <v>402</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
+        <v>164</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="F246" t="s">
-        <v>164</v>
-      </c>
-      <c r="G246" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,11 +7276,11 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="D247" t="s">
+      <c r="C247" t="s">
+        <v>95</v>
+      </c>
+      <c r="E247" t="s">
         <v>412</v>
-      </c>
-      <c r="E247" t="s">
-        <v>95</v>
       </c>
       <c r="F247" t="s">
         <v>96</v>
@@ -7296,11 +7296,11 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="D248" t="s">
+      <c r="C248" t="s">
+        <v>95</v>
+      </c>
+      <c r="E248" t="s">
         <v>412</v>
-      </c>
-      <c r="E248" t="s">
-        <v>95</v>
       </c>
       <c r="F248" t="s">
         <v>96</v>
@@ -7316,11 +7316,11 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="D249" t="s">
+      <c r="C249" t="s">
+        <v>415</v>
+      </c>
+      <c r="E249" t="s">
         <v>412</v>
-      </c>
-      <c r="E249" t="s">
-        <v>415</v>
       </c>
       <c r="F249" t="s">
         <v>96</v>
@@ -7336,11 +7336,11 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="D250" t="s">
+      <c r="C250" t="s">
+        <v>95</v>
+      </c>
+      <c r="E250" t="s">
         <v>412</v>
-      </c>
-      <c r="E250" t="s">
-        <v>95</v>
       </c>
       <c r="F250" t="s">
         <v>96</v>
@@ -7356,11 +7356,11 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="D251" t="s">
+      <c r="C251" t="s">
+        <v>95</v>
+      </c>
+      <c r="E251" t="s">
         <v>412</v>
-      </c>
-      <c r="E251" t="s">
-        <v>95</v>
       </c>
       <c r="F251" t="s">
         <v>96</v>
@@ -7376,11 +7376,11 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="D252" t="s">
+      <c r="C252" t="s">
+        <v>95</v>
+      </c>
+      <c r="E252" t="s">
         <v>412</v>
-      </c>
-      <c r="E252" t="s">
-        <v>95</v>
       </c>
       <c r="F252" t="s">
         <v>96</v>
@@ -7396,7 +7396,7 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="D253" t="s">
+      <c r="C253" t="s">
         <v>421</v>
       </c>
       <c r="E253" t="s">
@@ -7416,11 +7416,11 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="D254" t="s">
-        <v>421</v>
+      <c r="C254" t="s">
+        <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="F254" t="s">
         <v>92</v>
@@ -7436,11 +7436,11 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="D255" t="s">
-        <v>421</v>
+      <c r="C255" t="s">
+        <v>426</v>
       </c>
       <c r="E255" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F255" t="s">
         <v>92</v>
@@ -7456,11 +7456,11 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="D256" t="s">
-        <v>421</v>
+      <c r="C256" t="s">
+        <v>426</v>
       </c>
       <c r="E256" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F256" t="s">
         <v>92</v>
@@ -7476,11 +7476,11 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="D257" t="s">
-        <v>421</v>
+      <c r="C257" t="s">
+        <v>426</v>
       </c>
       <c r="E257" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F257" t="s">
         <v>92</v>
@@ -7496,11 +7496,11 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="D258" t="s">
-        <v>421</v>
+      <c r="C258" t="s">
+        <v>325</v>
       </c>
       <c r="E258" t="s">
-        <v>327</v>
+        <v>422</v>
       </c>
       <c r="F258" t="s">
         <v>164</v>
@@ -7516,11 +7516,11 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="D259" t="s">
-        <v>421</v>
+      <c r="C259" t="s">
+        <v>426</v>
       </c>
       <c r="E259" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F259" t="s">
         <v>92</v>
@@ -7536,11 +7536,11 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="D260" t="s">
-        <v>421</v>
+      <c r="C260" t="s">
+        <v>163</v>
       </c>
       <c r="E260" t="s">
-        <v>163</v>
+        <v>422</v>
       </c>
       <c r="F260" t="s">
         <v>164</v>
@@ -7556,11 +7556,11 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="D261" t="s">
-        <v>421</v>
+      <c r="C261" t="s">
+        <v>434</v>
       </c>
       <c r="E261" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="F261" t="s">
         <v>196</v>
@@ -7576,11 +7576,11 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="D262" t="s">
-        <v>421</v>
+      <c r="C262" t="s">
+        <v>163</v>
       </c>
       <c r="E262" t="s">
-        <v>163</v>
+        <v>422</v>
       </c>
       <c r="F262" t="s">
         <v>164</v>
@@ -7596,11 +7596,11 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="D263" t="s">
-        <v>421</v>
+      <c r="C263" t="s">
+        <v>438</v>
       </c>
       <c r="E263" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="F263" t="s">
         <v>183</v>
@@ -7616,11 +7616,11 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="D264" t="s">
-        <v>421</v>
+      <c r="C264" t="s">
+        <v>31</v>
       </c>
       <c r="E264" t="s">
-        <v>31</v>
+        <v>422</v>
       </c>
       <c r="F264" t="s">
         <v>32</v>
@@ -7636,11 +7636,11 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="D265" t="s">
-        <v>421</v>
+      <c r="C265" t="s">
+        <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>11</v>
+        <v>422</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7656,11 +7656,11 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="D266" t="s">
-        <v>421</v>
+      <c r="C266" t="s">
+        <v>443</v>
       </c>
       <c r="E266" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="F266" t="s">
         <v>115</v>
@@ -7676,11 +7676,11 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="D267" t="s">
+      <c r="C267" t="s">
+        <v>118</v>
+      </c>
+      <c r="E267" t="s">
         <v>446</v>
-      </c>
-      <c r="E267" t="s">
-        <v>118</v>
       </c>
       <c r="F267" t="s">
         <v>115</v>
@@ -7696,11 +7696,11 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="D268" t="s">
+      <c r="C268" t="s">
+        <v>202</v>
+      </c>
+      <c r="E268" t="s">
         <v>448</v>
-      </c>
-      <c r="E268" t="s">
-        <v>203</v>
       </c>
       <c r="F268" t="s">
         <v>183</v>
@@ -7716,11 +7716,11 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="D269" t="s">
+      <c r="C269" t="s">
+        <v>118</v>
+      </c>
+      <c r="E269" t="s">
         <v>450</v>
-      </c>
-      <c r="E269" t="s">
-        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>115</v>
@@ -7736,11 +7736,11 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="D270" t="s">
+      <c r="C270" t="s">
+        <v>118</v>
+      </c>
+      <c r="E270" t="s">
         <v>450</v>
-      </c>
-      <c r="E270" t="s">
-        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>115</v>
@@ -7756,7 +7756,7 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="D271" t="s">
+      <c r="C271" t="s">
         <v>453</v>
       </c>
       <c r="E271" t="s">
@@ -7776,7 +7776,7 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="D272" t="s">
+      <c r="C272" t="s">
         <v>453</v>
       </c>
       <c r="E272" t="s">
@@ -7796,7 +7796,7 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="D273" t="s">
+      <c r="C273" t="s">
         <v>453</v>
       </c>
       <c r="E273" t="s">
@@ -7816,7 +7816,7 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="D274" t="s">
+      <c r="C274" t="s">
         <v>453</v>
       </c>
       <c r="E274" t="s">
@@ -7836,7 +7836,7 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="D275" t="s">
+      <c r="C275" t="s">
         <v>453</v>
       </c>
       <c r="E275" t="s">
@@ -7856,7 +7856,7 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="D276" t="s">
+      <c r="C276" t="s">
         <v>453</v>
       </c>
       <c r="E276" t="s">
@@ -7876,7 +7876,7 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="D277" t="s">
+      <c r="C277" t="s">
         <v>453</v>
       </c>
       <c r="E277" t="s">
@@ -7896,11 +7896,11 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="D278" t="s">
+      <c r="C278" t="s">
+        <v>202</v>
+      </c>
+      <c r="E278" t="s">
         <v>463</v>
-      </c>
-      <c r="E278" t="s">
-        <v>203</v>
       </c>
       <c r="F278" t="s">
         <v>183</v>
@@ -7916,11 +7916,11 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="D279" t="s">
+      <c r="C279" t="s">
+        <v>51</v>
+      </c>
+      <c r="E279" t="s">
         <v>463</v>
-      </c>
-      <c r="E279" t="s">
-        <v>53</v>
       </c>
       <c r="F279" t="s">
         <v>32</v>
@@ -7936,11 +7936,11 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="D280" t="s">
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280" t="s">
         <v>463</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
@@ -7956,11 +7956,11 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="D281" t="s">
+      <c r="C281" t="s">
+        <v>170</v>
+      </c>
+      <c r="E281" t="s">
         <v>463</v>
-      </c>
-      <c r="E281" t="s">
-        <v>170</v>
       </c>
       <c r="F281" t="s">
         <v>115</v>
@@ -7976,11 +7976,11 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="D282" t="s">
+      <c r="C282" t="s">
+        <v>124</v>
+      </c>
+      <c r="E282" t="s">
         <v>463</v>
-      </c>
-      <c r="E282" t="s">
-        <v>124</v>
       </c>
       <c r="F282" t="s">
         <v>125</v>
@@ -7996,17 +7996,17 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="D283" t="s">
+      <c r="C283" t="s">
+        <v>363</v>
+      </c>
+      <c r="E283" t="s">
         <v>469</v>
       </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
+        <v>164</v>
+      </c>
+      <c r="G283" t="s">
         <v>399</v>
-      </c>
-      <c r="F283" t="s">
-        <v>164</v>
-      </c>
-      <c r="G283" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8016,11 +8016,11 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="D284" t="s">
+      <c r="C284" t="s">
+        <v>124</v>
+      </c>
+      <c r="E284" t="s">
         <v>471</v>
-      </c>
-      <c r="E284" t="s">
-        <v>124</v>
       </c>
       <c r="F284" t="s">
         <v>125</v>
@@ -8036,11 +8036,11 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="D285" t="s">
+      <c r="C285" t="s">
+        <v>170</v>
+      </c>
+      <c r="E285" t="s">
         <v>473</v>
-      </c>
-      <c r="E285" t="s">
-        <v>170</v>
       </c>
       <c r="F285" t="s">
         <v>115</v>
@@ -8056,11 +8056,11 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="D286" t="s">
+      <c r="C286" t="s">
+        <v>438</v>
+      </c>
+      <c r="E286" t="s">
         <v>475</v>
-      </c>
-      <c r="E286" t="s">
-        <v>438</v>
       </c>
       <c r="F286" t="s">
         <v>183</v>
@@ -8076,11 +8076,11 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="D287" t="s">
+      <c r="C287" t="s">
+        <v>438</v>
+      </c>
+      <c r="E287" t="s">
         <v>475</v>
-      </c>
-      <c r="E287" t="s">
-        <v>438</v>
       </c>
       <c r="F287" t="s">
         <v>183</v>
@@ -8096,11 +8096,11 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="D288" t="s">
+      <c r="C288" t="s">
+        <v>41</v>
+      </c>
+      <c r="E288" t="s">
         <v>475</v>
-      </c>
-      <c r="E288" t="s">
-        <v>41</v>
       </c>
       <c r="F288" t="s">
         <v>12</v>
@@ -8116,11 +8116,11 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="D289" t="s">
+      <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="E289" t="s">
         <v>475</v>
-      </c>
-      <c r="E289" t="s">
-        <v>31</v>
       </c>
       <c r="F289" t="s">
         <v>32</v>
@@ -8136,11 +8136,11 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="D290" t="s">
+      <c r="C290" t="s">
+        <v>31</v>
+      </c>
+      <c r="E290" t="s">
         <v>475</v>
-      </c>
-      <c r="E290" t="s">
-        <v>31</v>
       </c>
       <c r="F290" t="s">
         <v>32</v>
@@ -8156,11 +8156,11 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="D291" t="s">
+      <c r="C291" t="s">
+        <v>170</v>
+      </c>
+      <c r="E291" t="s">
         <v>475</v>
-      </c>
-      <c r="E291" t="s">
-        <v>170</v>
       </c>
       <c r="F291" t="s">
         <v>115</v>
@@ -8176,11 +8176,11 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="D292" t="s">
+      <c r="C292" t="s">
+        <v>170</v>
+      </c>
+      <c r="E292" t="s">
         <v>475</v>
-      </c>
-      <c r="E292" t="s">
-        <v>170</v>
       </c>
       <c r="F292" t="s">
         <v>115</v>
@@ -8196,11 +8196,11 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="D293" t="s">
+      <c r="C293" t="s">
+        <v>170</v>
+      </c>
+      <c r="E293" t="s">
         <v>475</v>
-      </c>
-      <c r="E293" t="s">
-        <v>170</v>
       </c>
       <c r="F293" t="s">
         <v>115</v>
@@ -8216,11 +8216,11 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="D294" t="s">
+      <c r="C294" t="s">
+        <v>170</v>
+      </c>
+      <c r="E294" t="s">
         <v>475</v>
-      </c>
-      <c r="E294" t="s">
-        <v>170</v>
       </c>
       <c r="F294" t="s">
         <v>115</v>
@@ -8236,11 +8236,11 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="D295" t="s">
+      <c r="C295" t="s">
+        <v>170</v>
+      </c>
+      <c r="E295" t="s">
         <v>485</v>
-      </c>
-      <c r="E295" t="s">
-        <v>170</v>
       </c>
       <c r="F295" t="s">
         <v>115</v>
@@ -8256,11 +8256,11 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="D296" t="s">
+      <c r="C296" t="s">
+        <v>170</v>
+      </c>
+      <c r="E296" t="s">
         <v>485</v>
-      </c>
-      <c r="E296" t="s">
-        <v>170</v>
       </c>
       <c r="F296" t="s">
         <v>115</v>

--- a/api/clv2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/clv2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1872,10 +1872,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1918,10 +1918,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1935,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,13 +1981,13 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2004,13 +2004,13 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,16 +2073,16 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2119,16 +2119,16 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,13 +2142,13 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2165,16 +2165,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2237,13 +2237,13 @@
         <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2260,13 +2260,13 @@
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
         <v>64</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" t="s">
         <v>64</v>
-      </c>
-      <c r="E23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
         <v>64</v>
-      </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
         <v>64</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
         <v>64</v>
-      </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
         <v>64</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
-      </c>
-      <c r="E28" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
         <v>64</v>
-      </c>
-      <c r="E29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,16 +2487,16 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
         <v>64</v>
-      </c>
-      <c r="E30" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
         <v>76</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
         <v>76</v>
-      </c>
-      <c r="E32" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
         <v>76</v>
-      </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
         <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
         <v>76</v>
-      </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" t="s">
         <v>76</v>
-      </c>
-      <c r="E36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2647,13 +2647,13 @@
       <c r="C37" t="s">
         <v>31</v>
       </c>
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2667,13 +2667,13 @@
       <c r="C38" t="s">
         <v>31</v>
       </c>
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
       <c r="C39" t="s">
         <v>31</v>
       </c>
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
       <c r="E39" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2707,13 +2707,13 @@
       <c r="C40" t="s">
         <v>31</v>
       </c>
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
       <c r="E40" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2727,14 +2727,14 @@
       <c r="C41" t="s">
         <v>51</v>
       </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2747,13 +2747,13 @@
       <c r="C42" t="s">
         <v>57</v>
       </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2767,13 +2767,13 @@
       <c r="C43" t="s">
         <v>90</v>
       </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2787,13 +2787,13 @@
       <c r="C44" t="s">
         <v>95</v>
       </c>
+      <c r="D44" t="s">
+        <v>91</v>
+      </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2807,13 +2807,13 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
       <c r="C46" t="s">
         <v>90</v>
       </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
       <c r="C47" t="s">
         <v>101</v>
       </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
-      </c>
-      <c r="G47" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2867,13 +2867,13 @@
       <c r="C48" t="s">
         <v>90</v>
       </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2887,13 +2887,13 @@
       <c r="C49" t="s">
         <v>90</v>
       </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2907,13 +2907,13 @@
       <c r="C50" t="s">
         <v>101</v>
       </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
       <c r="E50" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2927,13 +2927,13 @@
       <c r="C51" t="s">
         <v>90</v>
       </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2947,13 +2947,13 @@
       <c r="C52" t="s">
         <v>108</v>
       </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2967,14 +2967,14 @@
       <c r="C53" t="s">
         <v>9</v>
       </c>
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
       <c r="E53" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3017,10 +3017,10 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3040,10 +3040,10 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3060,13 +3060,13 @@
         <v>113</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3086,10 +3086,10 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3109,10 +3109,10 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3132,10 +3132,10 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3155,10 +3155,10 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3178,10 +3178,10 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
@@ -3201,10 +3201,10 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
@@ -3224,10 +3224,10 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3247,10 +3247,10 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3293,10 +3293,10 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3362,10 +3362,10 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3385,10 +3385,10 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3428,13 +3428,13 @@
         <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3451,13 +3451,13 @@
         <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3474,13 +3474,13 @@
         <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3497,13 +3497,13 @@
         <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3520,13 +3520,13 @@
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3543,13 +3543,13 @@
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3566,13 +3566,13 @@
         <v>113</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3589,13 +3589,13 @@
         <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3612,13 +3612,13 @@
         <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3635,13 +3635,13 @@
         <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3684,10 +3684,10 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
@@ -3707,10 +3707,10 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3727,13 +3727,13 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
@@ -3753,10 +3753,10 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,10 +3776,10 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3799,10 +3799,10 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3819,13 +3819,13 @@
         <v>113</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3842,13 +3842,13 @@
         <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3865,13 +3865,13 @@
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3891,10 +3891,10 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3911,13 +3911,13 @@
         <v>113</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3937,10 +3937,10 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
+        <v>125</v>
+      </c>
+      <c r="F96" t="s">
+        <v>126</v>
+      </c>
+      <c r="G96" t="s">
         <v>192</v>
-      </c>
-      <c r="E96" t="s">
-        <v>114</v>
-      </c>
-      <c r="F96" t="s">
-        <v>125</v>
-      </c>
-      <c r="G96" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
+        <v>125</v>
+      </c>
+      <c r="F97" t="s">
+        <v>126</v>
+      </c>
+      <c r="G97" t="s">
         <v>192</v>
-      </c>
-      <c r="E97" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" t="s">
-        <v>125</v>
-      </c>
-      <c r="G97" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F98" t="s">
+        <v>197</v>
+      </c>
+      <c r="G98" t="s">
         <v>192</v>
-      </c>
-      <c r="E98" t="s">
-        <v>114</v>
-      </c>
-      <c r="F98" t="s">
-        <v>196</v>
-      </c>
-      <c r="G98" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
+        <v>125</v>
+      </c>
+      <c r="F99" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" t="s">
         <v>192</v>
-      </c>
-      <c r="E99" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" t="s">
-        <v>125</v>
-      </c>
-      <c r="G99" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
+        <v>125</v>
+      </c>
+      <c r="F100" t="s">
+        <v>155</v>
+      </c>
+      <c r="G100" t="s">
         <v>192</v>
-      </c>
-      <c r="E100" t="s">
-        <v>114</v>
-      </c>
-      <c r="F100" t="s">
-        <v>125</v>
-      </c>
-      <c r="G100" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
+        <v>125</v>
+      </c>
+      <c r="F101" t="s">
+        <v>126</v>
+      </c>
+      <c r="G101" t="s">
         <v>192</v>
-      </c>
-      <c r="E101" t="s">
-        <v>114</v>
-      </c>
-      <c r="F101" t="s">
-        <v>125</v>
-      </c>
-      <c r="G101" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4091,13 +4091,13 @@
       <c r="C102" t="s">
         <v>202</v>
       </c>
+      <c r="D102" t="s">
+        <v>203</v>
+      </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
-      </c>
-      <c r="G102" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4111,13 +4111,13 @@
       <c r="C103" t="s">
         <v>202</v>
       </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F103" t="s">
-        <v>183</v>
-      </c>
-      <c r="G103" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4131,13 +4131,13 @@
       <c r="C104" t="s">
         <v>202</v>
       </c>
+      <c r="D104" t="s">
+        <v>203</v>
+      </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F104" t="s">
-        <v>183</v>
-      </c>
-      <c r="G104" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4151,13 +4151,13 @@
       <c r="C105" t="s">
         <v>208</v>
       </c>
+      <c r="D105" t="s">
+        <v>203</v>
+      </c>
       <c r="E105" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
-      </c>
-      <c r="G105" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4171,13 +4171,13 @@
       <c r="C106" t="s">
         <v>202</v>
       </c>
+      <c r="D106" t="s">
+        <v>203</v>
+      </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
-      </c>
-      <c r="G106" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4191,13 +4191,13 @@
       <c r="C107" t="s">
         <v>182</v>
       </c>
+      <c r="D107" t="s">
+        <v>203</v>
+      </c>
       <c r="E107" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F107" t="s">
-        <v>183</v>
-      </c>
-      <c r="G107" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4211,13 +4211,13 @@
       <c r="C108" t="s">
         <v>213</v>
       </c>
+      <c r="D108" t="s">
+        <v>203</v>
+      </c>
       <c r="E108" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F108" t="s">
-        <v>183</v>
-      </c>
-      <c r="G108" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="C109" t="s">
         <v>216</v>
       </c>
+      <c r="D109" t="s">
+        <v>203</v>
+      </c>
       <c r="E109" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
-      </c>
-      <c r="G109" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4251,13 +4251,13 @@
       <c r="C110" t="s">
         <v>219</v>
       </c>
+      <c r="D110" t="s">
+        <v>203</v>
+      </c>
       <c r="E110" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
-      </c>
-      <c r="G110" t="s">
         <v>220</v>
       </c>
     </row>
@@ -4271,13 +4271,13 @@
       <c r="C111" t="s">
         <v>202</v>
       </c>
+      <c r="D111" t="s">
+        <v>203</v>
+      </c>
       <c r="E111" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
-      </c>
-      <c r="G111" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4291,17 +4291,17 @@
       <c r="C112" t="s">
         <v>223</v>
       </c>
+      <c r="D112" t="s">
+        <v>203</v>
+      </c>
       <c r="E112" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
-      </c>
-      <c r="G112" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>143</v>
+      </c>
+      <c r="D113" t="s">
+        <v>203</v>
       </c>
       <c r="E113" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
-      <c r="G113" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4331,17 +4331,17 @@
       <c r="C114" t="s">
         <v>151</v>
       </c>
+      <c r="D114" t="s">
+        <v>203</v>
+      </c>
       <c r="E114" t="s">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
-      </c>
-      <c r="G114" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4351,17 +4351,17 @@
       <c r="C115" t="s">
         <v>182</v>
       </c>
+      <c r="D115" t="s">
+        <v>203</v>
+      </c>
       <c r="E115" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
-      </c>
-      <c r="G115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4371,17 +4371,17 @@
       <c r="C116" t="s">
         <v>230</v>
       </c>
+      <c r="D116" t="s">
+        <v>203</v>
+      </c>
       <c r="E116" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
-      </c>
-      <c r="G116" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4391,17 +4391,17 @@
       <c r="C117" t="s">
         <v>223</v>
       </c>
+      <c r="D117" t="s">
+        <v>203</v>
+      </c>
       <c r="E117" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
-      </c>
-      <c r="G117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>234</v>
+      </c>
+      <c r="D118" t="s">
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4431,17 +4431,17 @@
       <c r="C119" t="s">
         <v>182</v>
       </c>
+      <c r="D119" t="s">
+        <v>203</v>
+      </c>
       <c r="E119" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
-      </c>
-      <c r="G119" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4451,17 +4451,17 @@
       <c r="C120" t="s">
         <v>170</v>
       </c>
+      <c r="D120" t="s">
+        <v>237</v>
+      </c>
       <c r="E120" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F120" t="s">
-        <v>115</v>
-      </c>
-      <c r="G120" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>143</v>
+      </c>
+      <c r="D121" t="s">
+        <v>237</v>
       </c>
       <c r="E121" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
-      <c r="G121" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4491,17 +4491,17 @@
       <c r="C122" t="s">
         <v>170</v>
       </c>
+      <c r="D122" t="s">
+        <v>237</v>
+      </c>
       <c r="E122" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F122" t="s">
-        <v>115</v>
-      </c>
-      <c r="G122" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4511,17 +4511,17 @@
       <c r="C123" t="s">
         <v>170</v>
       </c>
+      <c r="D123" t="s">
+        <v>237</v>
+      </c>
       <c r="E123" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F123" t="s">
-        <v>115</v>
-      </c>
-      <c r="G123" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4531,17 +4531,17 @@
       <c r="C124" t="s">
         <v>242</v>
       </c>
+      <c r="D124" t="s">
+        <v>237</v>
+      </c>
       <c r="E124" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F124" t="s">
-        <v>164</v>
-      </c>
-      <c r="G124" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4551,17 +4551,17 @@
       <c r="C125" t="s">
         <v>242</v>
       </c>
+      <c r="D125" t="s">
+        <v>237</v>
+      </c>
       <c r="E125" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F125" t="s">
-        <v>164</v>
-      </c>
-      <c r="G125" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4571,17 +4571,17 @@
       <c r="C126" t="s">
         <v>242</v>
       </c>
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
       <c r="E126" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F126" t="s">
-        <v>164</v>
-      </c>
-      <c r="G126" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4591,17 +4591,17 @@
       <c r="C127" t="s">
         <v>242</v>
       </c>
+      <c r="D127" t="s">
+        <v>237</v>
+      </c>
       <c r="E127" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F127" t="s">
-        <v>164</v>
-      </c>
-      <c r="G127" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4611,13 +4611,13 @@
       <c r="C128" t="s">
         <v>242</v>
       </c>
+      <c r="D128" t="s">
+        <v>237</v>
+      </c>
       <c r="E128" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F128" t="s">
-        <v>164</v>
-      </c>
-      <c r="G128" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>249</v>
+      </c>
+      <c r="D129" t="s">
+        <v>237</v>
       </c>
       <c r="E129" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F129" t="s">
-        <v>164</v>
-      </c>
-      <c r="G129" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>251</v>
+      </c>
+      <c r="D130" t="s">
+        <v>237</v>
       </c>
       <c r="E130" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F130" t="s">
-        <v>164</v>
-      </c>
-      <c r="G130" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>253</v>
+      </c>
+      <c r="D131" t="s">
+        <v>237</v>
       </c>
       <c r="E131" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F131" t="s">
-        <v>164</v>
-      </c>
-      <c r="G131" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4691,13 +4691,13 @@
       <c r="C132" t="s">
         <v>255</v>
       </c>
+      <c r="D132" t="s">
+        <v>237</v>
+      </c>
       <c r="E132" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F132" t="s">
-        <v>164</v>
-      </c>
-      <c r="G132" t="s">
         <v>256</v>
       </c>
     </row>
@@ -4711,13 +4711,13 @@
       <c r="C133" t="s">
         <v>189</v>
       </c>
+      <c r="D133" t="s">
+        <v>237</v>
+      </c>
       <c r="E133" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F133" t="s">
-        <v>115</v>
-      </c>
-      <c r="G133" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
       <c r="C134" t="s">
         <v>175</v>
       </c>
+      <c r="D134" t="s">
+        <v>259</v>
+      </c>
       <c r="E134" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F134" t="s">
-        <v>164</v>
-      </c>
-      <c r="G134" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4751,13 +4751,13 @@
       <c r="C135" t="s">
         <v>175</v>
       </c>
+      <c r="D135" t="s">
+        <v>259</v>
+      </c>
       <c r="E135" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F135" t="s">
-        <v>164</v>
-      </c>
-      <c r="G135" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4771,13 +4771,13 @@
       <c r="C136" t="s">
         <v>175</v>
       </c>
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
       <c r="E136" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F136" t="s">
-        <v>164</v>
-      </c>
-      <c r="G136" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4791,13 +4791,13 @@
       <c r="C137" t="s">
         <v>175</v>
       </c>
+      <c r="D137" t="s">
+        <v>259</v>
+      </c>
       <c r="E137" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F137" t="s">
-        <v>164</v>
-      </c>
-      <c r="G137" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4811,13 +4811,13 @@
       <c r="C138" t="s">
         <v>175</v>
       </c>
+      <c r="D138" t="s">
+        <v>259</v>
+      </c>
       <c r="E138" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F138" t="s">
-        <v>164</v>
-      </c>
-      <c r="G138" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
       <c r="C139" t="s">
         <v>265</v>
       </c>
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
       <c r="E139" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="F139" t="s">
-        <v>224</v>
-      </c>
-      <c r="G139" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4851,13 +4851,13 @@
       <c r="C140" t="s">
         <v>175</v>
       </c>
+      <c r="D140" t="s">
+        <v>259</v>
+      </c>
       <c r="E140" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F140" t="s">
-        <v>164</v>
-      </c>
-      <c r="G140" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>164</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>164</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4921,13 +4921,13 @@
         <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4944,13 +4944,13 @@
         <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4967,13 +4967,13 @@
         <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>164</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5010,16 +5010,16 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
+        <v>270</v>
+      </c>
+      <c r="E147" t="s">
+        <v>164</v>
+      </c>
+      <c r="F147" t="s">
+        <v>271</v>
+      </c>
+      <c r="G147" t="s">
         <v>281</v>
-      </c>
-      <c r="E147" t="s">
-        <v>271</v>
-      </c>
-      <c r="F147" t="s">
-        <v>164</v>
-      </c>
-      <c r="G147" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5033,16 +5033,16 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
+        <v>270</v>
+      </c>
+      <c r="E148" t="s">
+        <v>164</v>
+      </c>
+      <c r="F148" t="s">
+        <v>271</v>
+      </c>
+      <c r="G148" t="s">
         <v>281</v>
-      </c>
-      <c r="E148" t="s">
-        <v>271</v>
-      </c>
-      <c r="F148" t="s">
-        <v>164</v>
-      </c>
-      <c r="G148" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5056,16 +5056,16 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
+        <v>270</v>
+      </c>
+      <c r="E149" t="s">
+        <v>164</v>
+      </c>
+      <c r="F149" t="s">
+        <v>271</v>
+      </c>
+      <c r="G149" t="s">
         <v>281</v>
-      </c>
-      <c r="E149" t="s">
-        <v>271</v>
-      </c>
-      <c r="F149" t="s">
-        <v>164</v>
-      </c>
-      <c r="G149" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5079,16 +5079,16 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
+        <v>270</v>
+      </c>
+      <c r="E150" t="s">
+        <v>164</v>
+      </c>
+      <c r="F150" t="s">
+        <v>271</v>
+      </c>
+      <c r="G150" t="s">
         <v>281</v>
-      </c>
-      <c r="E150" t="s">
-        <v>271</v>
-      </c>
-      <c r="F150" t="s">
-        <v>164</v>
-      </c>
-      <c r="G150" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5102,16 +5102,16 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
+        <v>270</v>
+      </c>
+      <c r="E151" t="s">
+        <v>164</v>
+      </c>
+      <c r="F151" t="s">
+        <v>271</v>
+      </c>
+      <c r="G151" t="s">
         <v>281</v>
-      </c>
-      <c r="E151" t="s">
-        <v>271</v>
-      </c>
-      <c r="F151" t="s">
-        <v>164</v>
-      </c>
-      <c r="G151" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5125,16 +5125,16 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
+        <v>270</v>
+      </c>
+      <c r="E152" t="s">
+        <v>164</v>
+      </c>
+      <c r="F152" t="s">
+        <v>271</v>
+      </c>
+      <c r="G152" t="s">
         <v>281</v>
-      </c>
-      <c r="E152" t="s">
-        <v>271</v>
-      </c>
-      <c r="F152" t="s">
-        <v>164</v>
-      </c>
-      <c r="G152" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5148,16 +5148,16 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
+        <v>270</v>
+      </c>
+      <c r="E153" t="s">
+        <v>164</v>
+      </c>
+      <c r="F153" t="s">
+        <v>271</v>
+      </c>
+      <c r="G153" t="s">
         <v>281</v>
-      </c>
-      <c r="E153" t="s">
-        <v>271</v>
-      </c>
-      <c r="F153" t="s">
-        <v>164</v>
-      </c>
-      <c r="G153" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5171,16 +5171,16 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
+        <v>270</v>
+      </c>
+      <c r="E154" t="s">
+        <v>164</v>
+      </c>
+      <c r="F154" t="s">
+        <v>271</v>
+      </c>
+      <c r="G154" t="s">
         <v>281</v>
-      </c>
-      <c r="E154" t="s">
-        <v>271</v>
-      </c>
-      <c r="F154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G154" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5194,16 +5194,16 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
+        <v>270</v>
+      </c>
+      <c r="E155" t="s">
+        <v>164</v>
+      </c>
+      <c r="F155" t="s">
+        <v>271</v>
+      </c>
+      <c r="G155" t="s">
         <v>281</v>
-      </c>
-      <c r="E155" t="s">
-        <v>271</v>
-      </c>
-      <c r="F155" t="s">
-        <v>164</v>
-      </c>
-      <c r="G155" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5217,16 +5217,16 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
+        <v>270</v>
+      </c>
+      <c r="E156" t="s">
+        <v>164</v>
+      </c>
+      <c r="F156" t="s">
+        <v>271</v>
+      </c>
+      <c r="G156" t="s">
         <v>291</v>
-      </c>
-      <c r="E156" t="s">
-        <v>271</v>
-      </c>
-      <c r="F156" t="s">
-        <v>164</v>
-      </c>
-      <c r="G156" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" t="s">
+        <v>164</v>
+      </c>
+      <c r="F157" t="s">
+        <v>271</v>
+      </c>
+      <c r="G157" t="s">
         <v>291</v>
-      </c>
-      <c r="E157" t="s">
-        <v>271</v>
-      </c>
-      <c r="F157" t="s">
-        <v>164</v>
-      </c>
-      <c r="G157" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,16 +5263,16 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
+        <v>270</v>
+      </c>
+      <c r="E158" t="s">
+        <v>164</v>
+      </c>
+      <c r="F158" t="s">
+        <v>271</v>
+      </c>
+      <c r="G158" t="s">
         <v>291</v>
-      </c>
-      <c r="E158" t="s">
-        <v>271</v>
-      </c>
-      <c r="F158" t="s">
-        <v>164</v>
-      </c>
-      <c r="G158" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5286,16 +5286,16 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
+        <v>270</v>
+      </c>
+      <c r="E159" t="s">
+        <v>164</v>
+      </c>
+      <c r="F159" t="s">
+        <v>271</v>
+      </c>
+      <c r="G159" t="s">
         <v>291</v>
-      </c>
-      <c r="E159" t="s">
-        <v>271</v>
-      </c>
-      <c r="F159" t="s">
-        <v>164</v>
-      </c>
-      <c r="G159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5309,16 +5309,16 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
+        <v>270</v>
+      </c>
+      <c r="E160" t="s">
+        <v>164</v>
+      </c>
+      <c r="F160" t="s">
+        <v>271</v>
+      </c>
+      <c r="G160" t="s">
         <v>291</v>
-      </c>
-      <c r="E160" t="s">
-        <v>271</v>
-      </c>
-      <c r="F160" t="s">
-        <v>164</v>
-      </c>
-      <c r="G160" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5332,16 +5332,16 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
+        <v>270</v>
+      </c>
+      <c r="E161" t="s">
+        <v>164</v>
+      </c>
+      <c r="F161" t="s">
+        <v>271</v>
+      </c>
+      <c r="G161" t="s">
         <v>291</v>
-      </c>
-      <c r="E161" t="s">
-        <v>271</v>
-      </c>
-      <c r="F161" t="s">
-        <v>164</v>
-      </c>
-      <c r="G161" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5355,16 +5355,16 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
+        <v>270</v>
+      </c>
+      <c r="E162" t="s">
+        <v>164</v>
+      </c>
+      <c r="F162" t="s">
+        <v>271</v>
+      </c>
+      <c r="G162" t="s">
         <v>299</v>
-      </c>
-      <c r="E162" t="s">
-        <v>271</v>
-      </c>
-      <c r="F162" t="s">
-        <v>164</v>
-      </c>
-      <c r="G162" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
+        <v>164</v>
+      </c>
+      <c r="F163" t="s">
         <v>271</v>
-      </c>
-      <c r="F163" t="s">
-        <v>164</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5401,16 +5401,16 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
+        <v>270</v>
+      </c>
+      <c r="E164" t="s">
+        <v>164</v>
+      </c>
+      <c r="F164" t="s">
+        <v>271</v>
+      </c>
+      <c r="G164" t="s">
         <v>304</v>
-      </c>
-      <c r="E164" t="s">
-        <v>271</v>
-      </c>
-      <c r="F164" t="s">
-        <v>164</v>
-      </c>
-      <c r="G164" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5424,16 +5424,16 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
+        <v>270</v>
+      </c>
+      <c r="E165" t="s">
+        <v>164</v>
+      </c>
+      <c r="F165" t="s">
+        <v>271</v>
+      </c>
+      <c r="G165" t="s">
         <v>304</v>
-      </c>
-      <c r="E165" t="s">
-        <v>271</v>
-      </c>
-      <c r="F165" t="s">
-        <v>164</v>
-      </c>
-      <c r="G165" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5447,16 +5447,16 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
+        <v>270</v>
+      </c>
+      <c r="E166" t="s">
+        <v>164</v>
+      </c>
+      <c r="F166" t="s">
+        <v>271</v>
+      </c>
+      <c r="G166" t="s">
         <v>304</v>
-      </c>
-      <c r="E166" t="s">
-        <v>271</v>
-      </c>
-      <c r="F166" t="s">
-        <v>164</v>
-      </c>
-      <c r="G166" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5470,16 +5470,16 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
+        <v>270</v>
+      </c>
+      <c r="E167" t="s">
+        <v>164</v>
+      </c>
+      <c r="F167" t="s">
+        <v>271</v>
+      </c>
+      <c r="G167" t="s">
         <v>304</v>
-      </c>
-      <c r="E167" t="s">
-        <v>271</v>
-      </c>
-      <c r="F167" t="s">
-        <v>164</v>
-      </c>
-      <c r="G167" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" t="s">
+        <v>164</v>
+      </c>
+      <c r="F168" t="s">
+        <v>271</v>
+      </c>
+      <c r="G168" t="s">
         <v>304</v>
-      </c>
-      <c r="E168" t="s">
-        <v>271</v>
-      </c>
-      <c r="F168" t="s">
-        <v>164</v>
-      </c>
-      <c r="G168" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
+        <v>270</v>
+      </c>
+      <c r="E169" t="s">
+        <v>164</v>
+      </c>
+      <c r="F169" t="s">
+        <v>271</v>
+      </c>
+      <c r="G169" t="s">
         <v>304</v>
-      </c>
-      <c r="E169" t="s">
-        <v>271</v>
-      </c>
-      <c r="F169" t="s">
-        <v>164</v>
-      </c>
-      <c r="G169" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
+        <v>270</v>
+      </c>
+      <c r="E170" t="s">
+        <v>164</v>
+      </c>
+      <c r="F170" t="s">
+        <v>271</v>
+      </c>
+      <c r="G170" t="s">
         <v>304</v>
-      </c>
-      <c r="E170" t="s">
-        <v>271</v>
-      </c>
-      <c r="F170" t="s">
-        <v>164</v>
-      </c>
-      <c r="G170" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5561,13 +5561,13 @@
       <c r="C171" t="s">
         <v>163</v>
       </c>
+      <c r="D171" t="s">
+        <v>313</v>
+      </c>
       <c r="E171" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5581,13 +5581,13 @@
       <c r="C172" t="s">
         <v>118</v>
       </c>
+      <c r="D172" t="s">
+        <v>313</v>
+      </c>
       <c r="E172" t="s">
-        <v>313</v>
+        <v>114</v>
       </c>
       <c r="F172" t="s">
-        <v>115</v>
-      </c>
-      <c r="G172" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5601,13 +5601,13 @@
       <c r="C173" t="s">
         <v>163</v>
       </c>
+      <c r="D173" t="s">
+        <v>313</v>
+      </c>
       <c r="E173" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5621,13 +5621,13 @@
       <c r="C174" t="s">
         <v>163</v>
       </c>
+      <c r="D174" t="s">
+        <v>313</v>
+      </c>
       <c r="E174" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5641,13 +5641,13 @@
       <c r="C175" t="s">
         <v>163</v>
       </c>
+      <c r="D175" t="s">
+        <v>313</v>
+      </c>
       <c r="E175" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5661,13 +5661,13 @@
       <c r="C176" t="s">
         <v>163</v>
       </c>
+      <c r="D176" t="s">
+        <v>313</v>
+      </c>
       <c r="E176" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5681,13 +5681,13 @@
       <c r="C177" t="s">
         <v>163</v>
       </c>
+      <c r="D177" t="s">
+        <v>320</v>
+      </c>
       <c r="E177" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5701,13 +5701,13 @@
       <c r="C178" t="s">
         <v>163</v>
       </c>
+      <c r="D178" t="s">
+        <v>320</v>
+      </c>
       <c r="E178" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5721,13 +5721,13 @@
       <c r="C179" t="s">
         <v>163</v>
       </c>
+      <c r="D179" t="s">
+        <v>320</v>
+      </c>
       <c r="E179" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5741,13 +5741,13 @@
       <c r="C180" t="s">
         <v>163</v>
       </c>
+      <c r="D180" t="s">
+        <v>320</v>
+      </c>
       <c r="E180" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5765,10 +5765,10 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>164</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
-      </c>
-      <c r="F181" t="s">
-        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5788,10 +5788,10 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>164</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
-      </c>
-      <c r="F182" t="s">
-        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5811,10 +5811,10 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>164</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
-      </c>
-      <c r="F183" t="s">
-        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5834,10 +5834,10 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>164</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
-      </c>
-      <c r="F184" t="s">
-        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5857,10 +5857,10 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>164</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5880,10 +5880,10 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>164</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
-      </c>
-      <c r="F186" t="s">
-        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5903,10 +5903,10 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>164</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5926,10 +5926,10 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>164</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
-      </c>
-      <c r="F188" t="s">
-        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5949,10 +5949,10 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>164</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
-      </c>
-      <c r="F189" t="s">
-        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5972,10 +5972,10 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>164</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5995,10 +5995,10 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>164</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6018,10 +6018,10 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>164</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F193" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,10 +6064,10 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>164</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
-      </c>
-      <c r="F194" t="s">
-        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6087,10 +6087,10 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>164</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6110,10 +6110,10 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>164</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6133,10 +6133,10 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>164</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
-      </c>
-      <c r="F197" t="s">
-        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6156,10 +6156,10 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>164</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
-      </c>
-      <c r="F198" t="s">
-        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
+        <v>164</v>
+      </c>
+      <c r="F199" t="s">
         <v>327</v>
-      </c>
-      <c r="F199" t="s">
-        <v>164</v>
       </c>
       <c r="G199" t="s">
         <v>349</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
+        <v>164</v>
+      </c>
+      <c r="F200" t="s">
         <v>327</v>
-      </c>
-      <c r="F200" t="s">
-        <v>164</v>
       </c>
       <c r="G200" t="s">
         <v>349</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
+        <v>164</v>
+      </c>
+      <c r="F201" t="s">
         <v>327</v>
-      </c>
-      <c r="F201" t="s">
-        <v>164</v>
       </c>
       <c r="G201" t="s">
         <v>349</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
+        <v>164</v>
+      </c>
+      <c r="F202" t="s">
         <v>327</v>
-      </c>
-      <c r="F202" t="s">
-        <v>164</v>
       </c>
       <c r="G202" t="s">
         <v>349</v>
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E203" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F203" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
+        <v>164</v>
+      </c>
+      <c r="F204" t="s">
         <v>327</v>
-      </c>
-      <c r="F204" t="s">
-        <v>164</v>
       </c>
       <c r="G204" t="s">
         <v>349</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
+        <v>164</v>
+      </c>
+      <c r="F205" t="s">
         <v>327</v>
-      </c>
-      <c r="F205" t="s">
-        <v>164</v>
       </c>
       <c r="G205" t="s">
         <v>357</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
+        <v>164</v>
+      </c>
+      <c r="F206" t="s">
         <v>327</v>
-      </c>
-      <c r="F206" t="s">
-        <v>164</v>
       </c>
       <c r="G206" t="s">
         <v>357</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
+        <v>164</v>
+      </c>
+      <c r="F207" t="s">
         <v>327</v>
-      </c>
-      <c r="F207" t="s">
-        <v>164</v>
       </c>
       <c r="G207" t="s">
         <v>357</v>
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E208" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F208" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
+        <v>164</v>
+      </c>
+      <c r="F209" t="s">
         <v>327</v>
-      </c>
-      <c r="F209" t="s">
-        <v>164</v>
       </c>
       <c r="G209" t="s">
         <v>357</v>
@@ -6432,10 +6432,10 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>164</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
-      </c>
-      <c r="F210" t="s">
-        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6455,10 +6455,10 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>164</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
-      </c>
-      <c r="F211" t="s">
-        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6478,10 +6478,10 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>164</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
-      </c>
-      <c r="F212" t="s">
-        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6501,10 +6501,10 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>164</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
-      </c>
-      <c r="F213" t="s">
-        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6524,10 +6524,10 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>164</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
-      </c>
-      <c r="F214" t="s">
-        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
         <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F215" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,10 +6570,10 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>164</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
-      </c>
-      <c r="F216" t="s">
-        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6593,10 +6593,10 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>164</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
-      </c>
-      <c r="F217" t="s">
-        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6616,10 +6616,10 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>164</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
-      </c>
-      <c r="F218" t="s">
-        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6639,10 +6639,10 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>164</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
-      </c>
-      <c r="F219" t="s">
-        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
         <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F220" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,10 +6685,10 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>164</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
-      </c>
-      <c r="F221" t="s">
-        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6708,10 +6708,10 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>164</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
-      </c>
-      <c r="F222" t="s">
-        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6731,10 +6731,10 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>164</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
-      </c>
-      <c r="F223" t="s">
-        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6754,10 +6754,10 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>164</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
-      </c>
-      <c r="F224" t="s">
-        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6777,10 +6777,10 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>164</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
-      </c>
-      <c r="F225" t="s">
-        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6800,13 +6800,13 @@
         <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,10 +6823,10 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>164</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
-      </c>
-      <c r="F227" t="s">
-        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6846,13 +6846,13 @@
         <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
+        <v>164</v>
+      </c>
+      <c r="F229" t="s">
         <v>365</v>
-      </c>
-      <c r="F229" t="s">
-        <v>164</v>
       </c>
       <c r="G229" t="s">
         <v>387</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
+        <v>164</v>
+      </c>
+      <c r="F230" t="s">
         <v>365</v>
-      </c>
-      <c r="F230" t="s">
-        <v>164</v>
       </c>
       <c r="G230" t="s">
         <v>387</v>
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E231" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F231" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E232" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F232" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
+        <v>164</v>
+      </c>
+      <c r="F233" t="s">
         <v>365</v>
-      </c>
-      <c r="F233" t="s">
-        <v>164</v>
       </c>
       <c r="G233" t="s">
         <v>387</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
+        <v>164</v>
+      </c>
+      <c r="F234" t="s">
         <v>365</v>
-      </c>
-      <c r="F234" t="s">
-        <v>164</v>
       </c>
       <c r="G234" t="s">
         <v>387</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
+        <v>164</v>
+      </c>
+      <c r="F235" t="s">
         <v>365</v>
-      </c>
-      <c r="F235" t="s">
-        <v>164</v>
       </c>
       <c r="G235" t="s">
         <v>387</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
+        <v>164</v>
+      </c>
+      <c r="F236" t="s">
         <v>365</v>
-      </c>
-      <c r="F236" t="s">
-        <v>164</v>
       </c>
       <c r="G236" t="s">
         <v>387</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
+        <v>164</v>
+      </c>
+      <c r="F237" t="s">
         <v>365</v>
-      </c>
-      <c r="F237" t="s">
-        <v>164</v>
       </c>
       <c r="G237" t="s">
         <v>387</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
+        <v>164</v>
+      </c>
+      <c r="F238" t="s">
         <v>365</v>
-      </c>
-      <c r="F238" t="s">
-        <v>164</v>
       </c>
       <c r="G238" t="s">
         <v>387</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
+        <v>164</v>
+      </c>
+      <c r="F239" t="s">
         <v>365</v>
-      </c>
-      <c r="F239" t="s">
-        <v>164</v>
       </c>
       <c r="G239" t="s">
         <v>399</v>
@@ -7122,13 +7122,13 @@
         <v>401</v>
       </c>
       <c r="E240" t="s">
+        <v>164</v>
+      </c>
+      <c r="F240" t="s">
+        <v>165</v>
+      </c>
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7145,13 +7145,13 @@
         <v>401</v>
       </c>
       <c r="E241" t="s">
+        <v>164</v>
+      </c>
+      <c r="F241" t="s">
+        <v>165</v>
+      </c>
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7168,13 +7168,13 @@
         <v>401</v>
       </c>
       <c r="E242" t="s">
+        <v>164</v>
+      </c>
+      <c r="F242" t="s">
+        <v>165</v>
+      </c>
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7191,13 +7191,13 @@
         <v>401</v>
       </c>
       <c r="E243" t="s">
+        <v>164</v>
+      </c>
+      <c r="F243" t="s">
+        <v>165</v>
+      </c>
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7214,13 +7214,13 @@
         <v>401</v>
       </c>
       <c r="E244" t="s">
+        <v>164</v>
+      </c>
+      <c r="F244" t="s">
+        <v>165</v>
+      </c>
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7237,13 +7237,13 @@
         <v>401</v>
       </c>
       <c r="E245" t="s">
+        <v>164</v>
+      </c>
+      <c r="F245" t="s">
+        <v>165</v>
+      </c>
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E246" t="s">
-        <v>402</v>
+        <v>164</v>
       </c>
       <c r="F246" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7279,13 +7279,13 @@
       <c r="C247" t="s">
         <v>95</v>
       </c>
+      <c r="D247" t="s">
+        <v>412</v>
+      </c>
       <c r="E247" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7299,13 +7299,13 @@
       <c r="C248" t="s">
         <v>95</v>
       </c>
+      <c r="D248" t="s">
+        <v>412</v>
+      </c>
       <c r="E248" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7319,13 +7319,13 @@
       <c r="C249" t="s">
         <v>415</v>
       </c>
+      <c r="D249" t="s">
+        <v>412</v>
+      </c>
       <c r="E249" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F249" t="s">
-        <v>96</v>
-      </c>
-      <c r="G249" t="s">
         <v>416</v>
       </c>
     </row>
@@ -7339,13 +7339,13 @@
       <c r="C250" t="s">
         <v>95</v>
       </c>
+      <c r="D250" t="s">
+        <v>412</v>
+      </c>
       <c r="E250" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
       <c r="C251" t="s">
         <v>95</v>
       </c>
+      <c r="D251" t="s">
+        <v>412</v>
+      </c>
       <c r="E251" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7379,13 +7379,13 @@
       <c r="C252" t="s">
         <v>95</v>
       </c>
+      <c r="D252" t="s">
+        <v>412</v>
+      </c>
       <c r="E252" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7399,13 +7399,13 @@
       <c r="C253" t="s">
         <v>421</v>
       </c>
+      <c r="D253" t="s">
+        <v>422</v>
+      </c>
       <c r="E253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F253" t="s">
-        <v>164</v>
-      </c>
-      <c r="G253" t="s">
         <v>423</v>
       </c>
     </row>
@@ -7419,13 +7419,13 @@
       <c r="C254" t="s">
         <v>219</v>
       </c>
+      <c r="D254" t="s">
+        <v>422</v>
+      </c>
       <c r="E254" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
-      </c>
-      <c r="G254" t="s">
         <v>220</v>
       </c>
     </row>
@@ -7439,13 +7439,13 @@
       <c r="C255" t="s">
         <v>426</v>
       </c>
+      <c r="D255" t="s">
+        <v>422</v>
+      </c>
       <c r="E255" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
-      </c>
-      <c r="G255" t="s">
         <v>427</v>
       </c>
     </row>
@@ -7459,17 +7459,17 @@
       <c r="C256" t="s">
         <v>426</v>
       </c>
+      <c r="D256" t="s">
+        <v>422</v>
+      </c>
       <c r="E256" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
-      </c>
-      <c r="G256" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7479,17 +7479,17 @@
       <c r="C257" t="s">
         <v>426</v>
       </c>
+      <c r="D257" t="s">
+        <v>422</v>
+      </c>
       <c r="E257" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
-      </c>
-      <c r="G257" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7499,17 +7499,17 @@
       <c r="C258" t="s">
         <v>325</v>
       </c>
+      <c r="D258" t="s">
+        <v>422</v>
+      </c>
       <c r="E258" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
-      </c>
-      <c r="G258" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7519,17 +7519,17 @@
       <c r="C259" t="s">
         <v>426</v>
       </c>
+      <c r="D259" t="s">
+        <v>422</v>
+      </c>
       <c r="E259" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
-      </c>
-      <c r="G259" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7539,17 +7539,17 @@
       <c r="C260" t="s">
         <v>163</v>
       </c>
+      <c r="D260" t="s">
+        <v>422</v>
+      </c>
       <c r="E260" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F260" t="s">
-        <v>164</v>
-      </c>
-      <c r="G260" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7559,17 +7559,17 @@
       <c r="C261" t="s">
         <v>434</v>
       </c>
+      <c r="D261" t="s">
+        <v>422</v>
+      </c>
       <c r="E261" t="s">
-        <v>422</v>
+        <v>196</v>
       </c>
       <c r="F261" t="s">
-        <v>196</v>
-      </c>
-      <c r="G261" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7579,17 +7579,17 @@
       <c r="C262" t="s">
         <v>163</v>
       </c>
+      <c r="D262" t="s">
+        <v>422</v>
+      </c>
       <c r="E262" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F262" t="s">
-        <v>164</v>
-      </c>
-      <c r="G262" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7599,17 +7599,17 @@
       <c r="C263" t="s">
         <v>438</v>
       </c>
+      <c r="D263" t="s">
+        <v>422</v>
+      </c>
       <c r="E263" t="s">
-        <v>422</v>
+        <v>183</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
-      </c>
-      <c r="G263" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7619,17 +7619,17 @@
       <c r="C264" t="s">
         <v>31</v>
       </c>
+      <c r="D264" t="s">
+        <v>422</v>
+      </c>
       <c r="E264" t="s">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
-      </c>
-      <c r="G264" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7639,17 +7639,17 @@
       <c r="C265" t="s">
         <v>9</v>
       </c>
+      <c r="D265" t="s">
+        <v>422</v>
+      </c>
       <c r="E265" t="s">
-        <v>422</v>
+        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
-      <c r="G265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7659,17 +7659,17 @@
       <c r="C266" t="s">
         <v>443</v>
       </c>
+      <c r="D266" t="s">
+        <v>422</v>
+      </c>
       <c r="E266" t="s">
-        <v>422</v>
+        <v>114</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
-      </c>
-      <c r="G266" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7679,17 +7679,17 @@
       <c r="C267" t="s">
         <v>118</v>
       </c>
+      <c r="D267" t="s">
+        <v>446</v>
+      </c>
       <c r="E267" t="s">
-        <v>446</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
-        <v>115</v>
-      </c>
-      <c r="G267" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7699,17 +7699,17 @@
       <c r="C268" t="s">
         <v>202</v>
       </c>
+      <c r="D268" t="s">
+        <v>448</v>
+      </c>
       <c r="E268" t="s">
-        <v>448</v>
+        <v>183</v>
       </c>
       <c r="F268" t="s">
-        <v>183</v>
-      </c>
-      <c r="G268" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7719,17 +7719,17 @@
       <c r="C269" t="s">
         <v>118</v>
       </c>
+      <c r="D269" t="s">
+        <v>450</v>
+      </c>
       <c r="E269" t="s">
-        <v>450</v>
+        <v>114</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
-      </c>
-      <c r="G269" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7739,17 +7739,17 @@
       <c r="C270" t="s">
         <v>118</v>
       </c>
+      <c r="D270" t="s">
+        <v>450</v>
+      </c>
       <c r="E270" t="s">
-        <v>450</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
-        <v>115</v>
-      </c>
-      <c r="G270" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7759,17 +7759,17 @@
       <c r="C271" t="s">
         <v>453</v>
       </c>
+      <c r="D271" t="s">
+        <v>454</v>
+      </c>
       <c r="E271" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F271" t="s">
-        <v>115</v>
-      </c>
-      <c r="G271" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7779,17 +7779,17 @@
       <c r="C272" t="s">
         <v>453</v>
       </c>
+      <c r="D272" t="s">
+        <v>454</v>
+      </c>
       <c r="E272" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F272" t="s">
-        <v>115</v>
-      </c>
-      <c r="G272" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7799,17 +7799,17 @@
       <c r="C273" t="s">
         <v>453</v>
       </c>
+      <c r="D273" t="s">
+        <v>454</v>
+      </c>
       <c r="E273" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F273" t="s">
-        <v>115</v>
-      </c>
-      <c r="G273" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7819,17 +7819,17 @@
       <c r="C274" t="s">
         <v>453</v>
       </c>
+      <c r="D274" t="s">
+        <v>454</v>
+      </c>
       <c r="E274" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F274" t="s">
-        <v>115</v>
-      </c>
-      <c r="G274" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7839,17 +7839,17 @@
       <c r="C275" t="s">
         <v>453</v>
       </c>
+      <c r="D275" t="s">
+        <v>454</v>
+      </c>
       <c r="E275" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F275" t="s">
-        <v>115</v>
-      </c>
-      <c r="G275" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7859,17 +7859,17 @@
       <c r="C276" t="s">
         <v>453</v>
       </c>
+      <c r="D276" t="s">
+        <v>454</v>
+      </c>
       <c r="E276" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
-        <v>115</v>
-      </c>
-      <c r="G276" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7879,17 +7879,17 @@
       <c r="C277" t="s">
         <v>453</v>
       </c>
+      <c r="D277" t="s">
+        <v>454</v>
+      </c>
       <c r="E277" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
-        <v>115</v>
-      </c>
-      <c r="G277" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7899,17 +7899,17 @@
       <c r="C278" t="s">
         <v>202</v>
       </c>
+      <c r="D278" t="s">
+        <v>463</v>
+      </c>
       <c r="E278" t="s">
-        <v>463</v>
+        <v>183</v>
       </c>
       <c r="F278" t="s">
-        <v>183</v>
-      </c>
-      <c r="G278" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7919,17 +7919,17 @@
       <c r="C279" t="s">
         <v>51</v>
       </c>
+      <c r="D279" t="s">
+        <v>463</v>
+      </c>
       <c r="E279" t="s">
-        <v>463</v>
+        <v>32</v>
       </c>
       <c r="F279" t="s">
-        <v>32</v>
-      </c>
-      <c r="G279" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7939,17 +7939,17 @@
       <c r="C280" t="s">
         <v>9</v>
       </c>
+      <c r="D280" t="s">
+        <v>463</v>
+      </c>
       <c r="E280" t="s">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
-      <c r="G280" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7959,17 +7959,17 @@
       <c r="C281" t="s">
         <v>170</v>
       </c>
+      <c r="D281" t="s">
+        <v>463</v>
+      </c>
       <c r="E281" t="s">
-        <v>463</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
-        <v>115</v>
-      </c>
-      <c r="G281" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7979,17 +7979,17 @@
       <c r="C282" t="s">
         <v>124</v>
       </c>
+      <c r="D282" t="s">
+        <v>463</v>
+      </c>
       <c r="E282" t="s">
-        <v>463</v>
+        <v>125</v>
       </c>
       <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
+        <v>398</v>
+      </c>
+      <c r="D283" t="s">
+        <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>469</v>
+        <v>164</v>
       </c>
       <c r="F283" t="s">
-        <v>164</v>
-      </c>
-      <c r="G283" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8019,17 +8019,17 @@
       <c r="C284" t="s">
         <v>124</v>
       </c>
+      <c r="D284" t="s">
+        <v>471</v>
+      </c>
       <c r="E284" t="s">
-        <v>471</v>
+        <v>125</v>
       </c>
       <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8039,17 +8039,17 @@
       <c r="C285" t="s">
         <v>170</v>
       </c>
+      <c r="D285" t="s">
+        <v>473</v>
+      </c>
       <c r="E285" t="s">
-        <v>473</v>
+        <v>114</v>
       </c>
       <c r="F285" t="s">
-        <v>115</v>
-      </c>
-      <c r="G285" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8059,17 +8059,17 @@
       <c r="C286" t="s">
         <v>438</v>
       </c>
+      <c r="D286" t="s">
+        <v>475</v>
+      </c>
       <c r="E286" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="F286" t="s">
-        <v>183</v>
-      </c>
-      <c r="G286" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8079,17 +8079,17 @@
       <c r="C287" t="s">
         <v>438</v>
       </c>
+      <c r="D287" t="s">
+        <v>475</v>
+      </c>
       <c r="E287" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="F287" t="s">
-        <v>183</v>
-      </c>
-      <c r="G287" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8099,17 +8099,17 @@
       <c r="C288" t="s">
         <v>41</v>
       </c>
+      <c r="D288" t="s">
+        <v>475</v>
+      </c>
       <c r="E288" t="s">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
-        <v>12</v>
-      </c>
-      <c r="G288" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8119,17 +8119,17 @@
       <c r="C289" t="s">
         <v>31</v>
       </c>
+      <c r="D289" t="s">
+        <v>475</v>
+      </c>
       <c r="E289" t="s">
-        <v>475</v>
+        <v>32</v>
       </c>
       <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8139,17 +8139,17 @@
       <c r="C290" t="s">
         <v>31</v>
       </c>
+      <c r="D290" t="s">
+        <v>475</v>
+      </c>
       <c r="E290" t="s">
-        <v>475</v>
+        <v>32</v>
       </c>
       <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8159,17 +8159,17 @@
       <c r="C291" t="s">
         <v>170</v>
       </c>
+      <c r="D291" t="s">
+        <v>475</v>
+      </c>
       <c r="E291" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F291" t="s">
-        <v>115</v>
-      </c>
-      <c r="G291" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8179,17 +8179,17 @@
       <c r="C292" t="s">
         <v>170</v>
       </c>
+      <c r="D292" t="s">
+        <v>475</v>
+      </c>
       <c r="E292" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F292" t="s">
-        <v>115</v>
-      </c>
-      <c r="G292" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8199,17 +8199,17 @@
       <c r="C293" t="s">
         <v>170</v>
       </c>
+      <c r="D293" t="s">
+        <v>475</v>
+      </c>
       <c r="E293" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F293" t="s">
-        <v>115</v>
-      </c>
-      <c r="G293" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8219,17 +8219,17 @@
       <c r="C294" t="s">
         <v>170</v>
       </c>
+      <c r="D294" t="s">
+        <v>475</v>
+      </c>
       <c r="E294" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F294" t="s">
-        <v>115</v>
-      </c>
-      <c r="G294" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8239,17 +8239,17 @@
       <c r="C295" t="s">
         <v>170</v>
       </c>
+      <c r="D295" t="s">
+        <v>485</v>
+      </c>
       <c r="E295" t="s">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="F295" t="s">
-        <v>115</v>
-      </c>
-      <c r="G295" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8259,13 +8259,13 @@
       <c r="C296" t="s">
         <v>170</v>
       </c>
+      <c r="D296" t="s">
+        <v>485</v>
+      </c>
       <c r="E296" t="s">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="F296" t="s">
-        <v>115</v>
-      </c>
-      <c r="G296" t="s">
         <v>171</v>
       </c>
     </row>
